--- a/docs/StructureDefinition-height.xlsx
+++ b/docs/StructureDefinition-height.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.6</t>
+    <t>0.5.8</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-height.xlsx
+++ b/docs/StructureDefinition-height.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.8</t>
+    <t>0.5.9</t>
   </si>
   <si>
     <t>Name</t>

--- a/docs/StructureDefinition-height.xlsx
+++ b/docs/StructureDefinition-height.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3699" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3699" uniqueCount="653">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.12</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -484,25 +484,29 @@
     <t>The position of the body when the observation was done, e.g. standing, sitting. To be used only when the body position in not precoordinated in the observation code.</t>
   </si>
   <si>
-    <t>Observation.extension:bodyPosition.id</t>
-  </si>
-  <si>
-    <t>Observation.extension.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
+    <t>Observation.extension:bodyPosition.id</t>
+  </si>
+  <si>
+    <t>Observation.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -552,7 +556,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
     <t xml:space="preserve">type:$this}
@@ -565,10 +569,6 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">ext-1
-</t>
-  </si>
-  <si>
     <t>Observation.extension:bodyPosition.value[x]:valueCodeableConcept</t>
   </si>
   <si>
@@ -823,10 +823,6 @@
   </si>
   <si>
     <t>Observation.category.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
   </si>
   <si>
     <t>Observation.category:VSCat.extension</t>
@@ -3597,7 +3593,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>144</v>
@@ -3623,10 +3619,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3649,13 +3645,13 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3706,7 +3702,7 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -3715,7 +3711,7 @@
         <v>93</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>20</v>
@@ -3730,7 +3726,7 @@
         <v>20</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>20</v>
@@ -3741,10 +3737,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3815,7 +3811,7 @@
         <v>141</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>20</v>
@@ -3824,7 +3820,7 @@
         <v>142</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3859,10 +3855,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3888,13 +3884,13 @@
         <v>107</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3902,7 +3898,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>20</v>
@@ -3944,7 +3940,7 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>93</v>
@@ -3979,10 +3975,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4005,13 +4001,13 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4050,17 +4046,17 @@
         <v>20</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC14" s="2"/>
       <c r="AD14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4069,7 +4065,7 @@
         <v>93</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>105</v>
@@ -4098,7 +4094,7 @@
         <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" t="s" s="2">
         <v>178</v>
@@ -4123,13 +4119,13 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4178,7 +4174,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4187,7 +4183,7 @@
         <v>93</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>105</v>
@@ -4307,7 +4303,7 @@
         <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>144</v>
@@ -4336,7 +4332,7 @@
         <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4359,13 +4355,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>95</v>
+        <v>153</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4416,7 +4412,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4425,7 +4421,7 @@
         <v>93</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>155</v>
+        <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>20</v>
@@ -4440,7 +4436,7 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -4454,7 +4450,7 @@
         <v>187</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4525,7 +4521,7 @@
         <v>141</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
@@ -4534,7 +4530,7 @@
         <v>142</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4572,7 +4568,7 @@
         <v>188</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4598,13 +4594,13 @@
         <v>107</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4654,7 +4650,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>93</v>
@@ -4692,7 +4688,7 @@
         <v>190</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4715,13 +4711,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4758,17 +4754,17 @@
         <v>20</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC20" s="2"/>
       <c r="AD20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4777,7 +4773,7 @@
         <v>93</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>105</v>
@@ -4806,7 +4802,7 @@
         <v>193</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C21" t="s" s="2">
         <v>178</v>
@@ -4831,13 +4827,13 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4886,7 +4882,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4895,7 +4891,7 @@
         <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>105</v>
@@ -5669,7 +5665,7 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>246</v>
@@ -5791,7 +5787,7 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>246</v>
@@ -5913,13 +5909,13 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5970,7 +5966,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5994,7 +5990,7 @@
         <v>20</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>20</v>
@@ -6005,10 +6001,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>261</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6034,10 +6030,10 @@
         <v>138</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N31" t="s" s="2">
         <v>203</v>
@@ -6081,7 +6077,7 @@
         <v>141</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>20</v>
@@ -6090,7 +6086,7 @@
         <v>142</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6114,7 +6110,7 @@
         <v>20</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -6125,10 +6121,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6151,19 +6147,19 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="M32" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -6212,7 +6208,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6233,10 +6229,10 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -6247,10 +6243,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6273,13 +6269,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6330,7 +6326,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6354,7 +6350,7 @@
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
@@ -6365,10 +6361,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>277</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6394,10 +6390,10 @@
         <v>138</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N34" t="s" s="2">
         <v>203</v>
@@ -6441,7 +6437,7 @@
         <v>141</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>20</v>
@@ -6450,7 +6446,7 @@
         <v>142</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6474,7 +6470,7 @@
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6485,10 +6481,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>279</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6514,65 +6510,65 @@
         <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6593,10 +6589,10 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6607,10 +6603,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6633,16 +6629,16 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6692,7 +6688,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6713,10 +6709,10 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6727,10 +6723,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6756,63 +6752,63 @@
         <v>113</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M37" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="S37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6833,10 +6829,10 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6847,10 +6843,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>306</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6873,17 +6869,17 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6932,7 +6928,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6953,10 +6949,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6967,10 +6963,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="B39" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6993,19 +6989,19 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -7054,7 +7050,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -7075,10 +7071,10 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -7089,10 +7085,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B40" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7115,19 +7111,19 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M40" t="s" s="2">
+      <c r="N40" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -7176,7 +7172,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7197,10 +7193,10 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -7211,14 +7207,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7237,19 +7233,19 @@
         <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M41" t="s" s="2">
+      <c r="N41" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -7277,11 +7273,11 @@
         <v>179</v>
       </c>
       <c r="Y41" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="Z41" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="Z41" t="s" s="2">
-        <v>339</v>
-      </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
       </c>
@@ -7298,7 +7294,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>93</v>
@@ -7313,30 +7309,30 @@
         <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AN41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>343</v>
       </c>
-      <c r="AO41" t="s" s="2">
+      <c r="AP41" t="s" s="2">
         <v>344</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>345</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7359,13 +7355,13 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7416,7 +7412,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7440,7 +7436,7 @@
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7451,10 +7447,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7480,10 +7476,10 @@
         <v>138</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>203</v>
@@ -7527,7 +7523,7 @@
         <v>141</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>20</v>
@@ -7536,7 +7532,7 @@
         <v>142</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7560,7 +7556,7 @@
         <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
@@ -7571,10 +7567,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7597,19 +7593,19 @@
         <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L44" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L44" t="s" s="2">
+      <c r="M44" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7646,7 +7642,7 @@
         <v>20</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
@@ -7656,7 +7652,7 @@
         <v>142</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7677,10 +7673,10 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7691,13 +7687,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="C45" t="s" s="2">
         <v>350</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>351</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>20</v>
@@ -7719,19 +7715,19 @@
         <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -7780,7 +7776,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7801,10 +7797,10 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AN45" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7815,10 +7811,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7841,13 +7837,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7898,7 +7894,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7922,7 +7918,7 @@
         <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7933,10 +7929,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7962,10 +7958,10 @@
         <v>138</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>203</v>
@@ -8009,7 +8005,7 @@
         <v>141</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>20</v>
@@ -8018,7 +8014,7 @@
         <v>142</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8042,7 +8038,7 @@
         <v>20</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -8053,10 +8049,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8082,23 +8078,23 @@
         <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>20</v>
@@ -8140,7 +8136,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8161,10 +8157,10 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -8175,10 +8171,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>359</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>360</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8201,16 +8197,16 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8260,7 +8256,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8281,10 +8277,10 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -8295,10 +8291,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8324,21 +8320,21 @@
         <v>113</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>20</v>
@@ -8380,7 +8376,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8401,10 +8397,10 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -8415,10 +8411,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B51" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8441,17 +8437,17 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>308</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>20</v>
@@ -8500,7 +8496,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8521,10 +8517,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8535,10 +8531,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B52" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8561,19 +8557,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -8622,7 +8618,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8643,10 +8639,10 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8657,10 +8653,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8683,19 +8679,19 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="N53" t="s" s="2">
+      <c r="O53" t="s" s="2">
         <v>327</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8744,7 +8740,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8765,10 +8761,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AN53" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>331</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8779,10 +8775,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8805,19 +8801,19 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8866,7 +8862,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8881,19 +8877,19 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>20</v>
@@ -8901,10 +8897,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8927,16 +8923,16 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>383</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8986,7 +8982,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9007,13 +9003,13 @@
         <v>20</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>20</v>
@@ -9021,14 +9017,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -9047,19 +9043,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -9108,7 +9104,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9123,19 +9119,19 @@
         <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>20</v>
@@ -9143,14 +9139,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9169,19 +9165,19 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="N57" t="s" s="2">
+      <c r="O57" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>402</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -9230,7 +9226,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9239,25 +9235,25 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AJ57" t="s" s="2">
+      <c r="AK57" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AK57" t="s" s="2">
+      <c r="AL57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>20</v>
@@ -9265,10 +9261,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9291,16 +9287,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
         <v>411</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9350,7 +9346,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9371,13 +9367,13 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AN58" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>416</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>20</v>
@@ -9385,10 +9381,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9411,17 +9407,17 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>420</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9470,7 +9466,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9485,19 +9481,19 @@
         <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AL59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>20</v>
@@ -9505,10 +9501,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9531,19 +9527,19 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="M60" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N60" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M60" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9580,17 +9576,17 @@
         <v>20</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9599,7 +9595,7 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9608,30 +9604,30 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AN60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP60" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP60" t="s" s="2">
-        <v>435</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C61" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="D61" t="s" s="2">
         <v>20</v>
@@ -9653,19 +9649,19 @@
         <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M61" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N61" t="s" s="2">
+      <c r="O61" t="s" s="2">
         <v>429</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>430</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9714,7 +9710,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9723,7 +9719,7 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9732,27 +9728,27 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM61" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AM61" t="s" s="2">
+      <c r="AN61" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AO61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP61" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP61" t="s" s="2">
-        <v>435</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9775,13 +9771,13 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9832,7 +9828,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9856,7 +9852,7 @@
         <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>20</v>
@@ -9867,10 +9863,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>440</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9896,10 +9892,10 @@
         <v>138</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>203</v>
@@ -9943,7 +9939,7 @@
         <v>141</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>20</v>
@@ -9952,7 +9948,7 @@
         <v>142</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9976,7 +9972,7 @@
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>20</v>
@@ -9987,10 +9983,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B64" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10013,19 +10009,19 @@
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L64" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L64" t="s" s="2">
+      <c r="M64" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="M64" t="s" s="2">
+      <c r="N64" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="N64" t="s" s="2">
+      <c r="O64" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -10074,7 +10070,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10095,10 +10091,10 @@
         <v>20</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>20</v>
@@ -10109,10 +10105,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B65" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10138,20 +10134,20 @@
         <v>113</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q65" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="P65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q65" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="R65" t="s" s="2">
         <v>20</v>
@@ -10175,28 +10171,28 @@
         <v>238</v>
       </c>
       <c r="Y65" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="Z65" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="Z65" t="s" s="2">
+      <c r="AA65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10217,10 +10213,10 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN65" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -10231,10 +10227,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B66" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10257,17 +10253,17 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -10316,7 +10312,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10337,10 +10333,10 @@
         <v>20</v>
       </c>
       <c r="AM66" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AN66" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
@@ -10351,10 +10347,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10380,72 +10376,72 @@
         <v>107</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="M67" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF67" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="S67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE67" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF67" t="s" s="2">
+      <c r="AG67" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI67" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AG67" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH67" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI67" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10457,10 +10453,10 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10471,10 +10467,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="B68" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10500,16 +10496,16 @@
         <v>113</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="M68" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>483</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>484</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10538,25 +10534,25 @@
       </c>
       <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10577,10 +10573,10 @@
         <v>20</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
@@ -10591,10 +10587,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10617,19 +10613,19 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M69" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10657,37 +10653,37 @@
         <v>179</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z69" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="Z69" t="s" s="2">
+      <c r="AA69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI69" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="AG69" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH69" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI69" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>105</v>
@@ -10702,7 +10698,7 @@
         <v>136</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -10713,14 +10709,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10739,19 +10735,19 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="N70" t="s" s="2">
+      <c r="O70" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -10780,7 +10776,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
@@ -10798,7 +10794,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10816,27 +10812,27 @@
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>507</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10859,19 +10855,19 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="L71" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="L71" t="s" s="2">
+      <c r="M71" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>512</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>513</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10920,7 +10916,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10941,10 +10937,10 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -10955,10 +10951,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10981,16 +10977,16 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L72" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M72" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11019,11 +11015,11 @@
         <v>191</v>
       </c>
       <c r="Y72" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="Z72" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="Z72" t="s" s="2">
-        <v>521</v>
-      </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
       </c>
@@ -11040,7 +11036,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11058,27 +11054,27 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>525</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11101,19 +11097,19 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L73" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M73" t="s" s="2">
         <v>527</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="N73" t="s" s="2">
+      <c r="O73" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -11142,7 +11138,7 @@
       </c>
       <c r="Y73" s="2"/>
       <c r="Z73" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>20</v>
@@ -11160,7 +11156,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11181,10 +11177,10 @@
         <v>20</v>
       </c>
       <c r="AM73" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
@@ -11195,10 +11191,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11221,16 +11217,16 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11280,7 +11276,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11298,27 +11294,27 @@
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="AN74" t="s" s="2">
+      <c r="AO74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP74" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="AO74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP74" t="s" s="2">
-        <v>542</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11341,16 +11337,16 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="L75" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="L75" t="s" s="2">
+      <c r="M75" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="M75" t="s" s="2">
+      <c r="N75" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11400,7 +11396,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -11418,27 +11414,27 @@
         <v>20</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AM75" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="AM75" t="s" s="2">
+      <c r="AN75" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AN75" t="s" s="2">
+      <c r="AO75" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP75" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="AO75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP75" t="s" s="2">
-        <v>551</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11461,19 +11457,19 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L76" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="L76" t="s" s="2">
+      <c r="M76" t="s" s="2">
         <v>554</v>
       </c>
-      <c r="M76" t="s" s="2">
+      <c r="N76" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="N76" t="s" s="2">
+      <c r="O76" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>20</v>
@@ -11522,7 +11518,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -11534,19 +11530,19 @@
         <v>20</v>
       </c>
       <c r="AJ76" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM76" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="AK76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM76" t="s" s="2">
+      <c r="AN76" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
@@ -11557,10 +11553,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11583,13 +11579,13 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11640,7 +11636,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11664,7 +11660,7 @@
         <v>20</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>20</v>
@@ -11675,10 +11671,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11704,10 +11700,10 @@
         <v>138</v>
       </c>
       <c r="L78" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M78" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N78" t="s" s="2">
         <v>203</v>
@@ -11760,7 +11756,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11784,7 +11780,7 @@
         <v>20</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -11795,14 +11791,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11824,10 +11820,10 @@
         <v>138</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="N79" t="s" s="2">
         <v>203</v>
@@ -11882,7 +11878,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11917,10 +11913,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11943,13 +11939,13 @@
         <v>20</v>
       </c>
       <c r="K80" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L80" t="s" s="2">
         <v>569</v>
       </c>
-      <c r="L80" t="s" s="2">
+      <c r="M80" t="s" s="2">
         <v>570</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>571</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -12000,7 +11996,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12009,7 +12005,7 @@
         <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>105</v>
@@ -12021,10 +12017,10 @@
         <v>20</v>
       </c>
       <c r="AM80" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -12035,10 +12031,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12061,13 +12057,13 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12118,7 +12114,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12127,7 +12123,7 @@
         <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>105</v>
@@ -12139,10 +12135,10 @@
         <v>20</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -12153,10 +12149,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12179,19 +12175,19 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="M82" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="N82" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="N82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -12219,11 +12215,11 @@
         <v>117</v>
       </c>
       <c r="Y82" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="Z82" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="Z82" t="s" s="2">
-        <v>585</v>
-      </c>
       <c r="AA82" t="s" s="2">
         <v>20</v>
       </c>
@@ -12240,7 +12236,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12258,13 +12254,13 @@
         <v>20</v>
       </c>
       <c r="AL82" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AM82" t="s" s="2">
-        <v>587</v>
-      </c>
       <c r="AN82" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>20</v>
@@ -12275,10 +12271,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12301,19 +12297,19 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="M83" t="s" s="2">
+      <c r="N83" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="N83" t="s" s="2">
+      <c r="O83" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>20</v>
@@ -12341,11 +12337,11 @@
         <v>191</v>
       </c>
       <c r="Y83" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="Z83" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="Z83" t="s" s="2">
-        <v>594</v>
-      </c>
       <c r="AA83" t="s" s="2">
         <v>20</v>
       </c>
@@ -12362,7 +12358,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12380,13 +12376,13 @@
         <v>20</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AM83" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="AM83" t="s" s="2">
-        <v>587</v>
-      </c>
       <c r="AN83" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
@@ -12397,10 +12393,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12423,17 +12419,17 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>598</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>20</v>
@@ -12482,7 +12478,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12506,7 +12502,7 @@
         <v>20</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
@@ -12517,10 +12513,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12543,13 +12539,13 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>602</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>603</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -12600,7 +12596,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12621,10 +12617,10 @@
         <v>20</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -12635,10 +12631,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12661,16 +12657,16 @@
         <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="L86" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="L86" t="s" s="2">
+      <c r="M86" t="s" s="2">
         <v>607</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>608</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>609</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12720,7 +12716,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12741,10 +12737,10 @@
         <v>20</v>
       </c>
       <c r="AM86" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AN86" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -12755,10 +12751,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12781,16 +12777,16 @@
         <v>94</v>
       </c>
       <c r="K87" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="L87" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="L87" t="s" s="2">
+      <c r="M87" t="s" s="2">
         <v>614</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12840,7 +12836,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12861,10 +12857,10 @@
         <v>20</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -12875,10 +12871,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12901,19 +12897,19 @@
         <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="L88" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="M88" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>20</v>
@@ -12962,7 +12958,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -12974,19 +12970,19 @@
         <v>20</v>
       </c>
       <c r="AJ88" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM88" t="s" s="2">
         <v>622</v>
       </c>
-      <c r="AK88" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM88" t="s" s="2">
+      <c r="AN88" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>20</v>
@@ -12997,10 +12993,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13023,13 +13019,13 @@
         <v>20</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>259</v>
+        <v>153</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -13080,7 +13076,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13104,7 +13100,7 @@
         <v>20</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>20</v>
@@ -13115,10 +13111,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13144,10 +13140,10 @@
         <v>138</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>203</v>
@@ -13200,7 +13196,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -13224,7 +13220,7 @@
         <v>20</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>20</v>
@@ -13235,14 +13231,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -13264,10 +13260,10 @@
         <v>138</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>203</v>
@@ -13322,7 +13318,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13357,10 +13353,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13383,19 +13379,19 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="N92" t="s" s="2">
+      <c r="O92" t="s" s="2">
         <v>631</v>
-      </c>
-      <c r="O92" t="s" s="2">
-        <v>632</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>20</v>
@@ -13423,11 +13419,11 @@
         <v>179</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>339</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>20</v>
       </c>
@@ -13444,7 +13440,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>93</v>
@@ -13462,16 +13458,16 @@
         <v>20</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="AM92" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AN92" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AN92" t="s" s="2">
+      <c r="AO92" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>20</v>
@@ -13479,10 +13475,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13505,19 +13501,19 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="L93" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="M93" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="N93" t="s" s="2">
-        <v>638</v>
-      </c>
       <c r="O93" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>20</v>
@@ -13545,37 +13541,37 @@
         <v>179</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="Z93" t="s" s="2">
+      <c r="AA93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI93" t="s" s="2">
         <v>640</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="AG93" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH93" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI93" t="s" s="2">
-        <v>641</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>105</v>
@@ -13584,27 +13580,27 @@
         <v>20</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AM93" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="AN93" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>435</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13627,19 +13623,19 @@
         <v>20</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="N94" t="s" s="2">
-        <v>646</v>
-      </c>
       <c r="O94" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -13667,11 +13663,11 @@
         <v>179</v>
       </c>
       <c r="Y94" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="Z94" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="Z94" t="s" s="2">
-        <v>494</v>
-      </c>
       <c r="AA94" t="s" s="2">
         <v>20</v>
       </c>
@@ -13688,7 +13684,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13697,7 +13693,7 @@
         <v>93</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>105</v>
@@ -13712,7 +13708,7 @@
         <v>136</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>20</v>
@@ -13723,14 +13719,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13749,19 +13745,19 @@
         <v>20</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="N95" t="s" s="2">
+      <c r="O95" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -13789,11 +13785,11 @@
         <v>179</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="Z95" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="Z95" t="s" s="2">
-        <v>650</v>
-      </c>
       <c r="AA95" t="s" s="2">
         <v>20</v>
       </c>
@@ -13810,7 +13806,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -13828,27 +13824,27 @@
         <v>20</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>504</v>
       </c>
-      <c r="AM95" t="s" s="2">
+      <c r="AN95" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="AN95" t="s" s="2">
+      <c r="AO95" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AP95" t="s" s="2">
         <v>506</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>507</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13874,16 +13870,16 @@
         <v>20</v>
       </c>
       <c r="L96" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="M96" t="s" s="2">
-        <v>653</v>
-      </c>
       <c r="N96" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="O96" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>20</v>
@@ -13932,7 +13928,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -13953,10 +13949,10 @@
         <v>20</v>
       </c>
       <c r="AM96" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-height.xlsx
+++ b/docs/StructureDefinition-height.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
